--- a/CTEHE2019/Proyectos/EjemploI_2526_Option1_Config1/ejemploi_2526_option1_config1.xlsx
+++ b/CTEHE2019/Proyectos/EjemploI_2526_Option1_Config1/ejemploi_2526_option1_config1.xlsx
@@ -8,19 +8,33 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ProyectosCTEyCEE\CTEHE2019\Proyectos\EjemploI_2526_Option1_Config1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{18F6112C-02A7-4482-B423-58F21B05D7F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D5A74F9-66E2-4CB9-9A32-4D6A50D6D5FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2244" yWindow="4752" windowWidth="22536" windowHeight="19056" xr2:uid="{3B09A6EE-9EE8-4827-B081-3758E53C1BFB}"/>
+    <workbookView xWindow="12920" yWindow="0" windowWidth="18280" windowHeight="17600" activeTab="1" xr2:uid="{3B09A6EE-9EE8-4827-B081-3758E53C1BFB}"/>
   </bookViews>
   <sheets>
     <sheet name="ejemploi_2526_option1_config1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="55">
   <si>
     <t>ProyectoEdificio</t>
   </si>
@@ -170,6 +184,21 @@
   </si>
   <si>
     <t>hours/day</t>
+  </si>
+  <si>
+    <t>Month</t>
+  </si>
+  <si>
+    <t>demandaACS (kWh)</t>
+  </si>
+  <si>
+    <t>demandaCAL (kWh)</t>
+  </si>
+  <si>
+    <t>demandaREF (kWh)</t>
+  </si>
+  <si>
+    <t>H(i)_m (kWh/m2/mo)</t>
   </si>
 </sst>
 </file>
@@ -178,7 +207,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
   <fonts count="20" x14ac:knownFonts="1">
     <font>
@@ -330,7 +359,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="35">
+  <fills count="36">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -519,6 +548,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -693,24 +728,28 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="165" fontId="0" fillId="33" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="33" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="43" fontId="0" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="165" fontId="0" fillId="34" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="34" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="16" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="16" fillId="34" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="33" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="34" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="33" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="34" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="43" fontId="6" fillId="2" borderId="0" xfId="7" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="16" fillId="35" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="35" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="43">
     <cellStyle name="20% - Accent1" xfId="20" builtinId="30" customBuiltin="1"/>
@@ -768,6 +807,55 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>45771</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>31960</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{026E5ECE-19BE-CB3E-7849-E679C0CAC197}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1314450" y="6629400"/>
+          <a:ext cx="9469171" cy="1505160"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1088,17 +1176,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C0DA73A8-5D75-4D35-BF5D-6ED116870A7D}">
   <dimension ref="A1:P33"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="18.77734375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="12" width="12.21875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.109375" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="10.21875" style="12" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="9.21875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.08984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="12" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.08984375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="10.1796875" style="12" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="9.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1109,7 +1197,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A3" s="8" t="s">
         <v>3</v>
       </c>
@@ -1117,7 +1205,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A4" s="8" t="s">
         <v>5</v>
       </c>
@@ -1131,7 +1219,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A5" s="8" t="s">
         <v>7</v>
       </c>
@@ -1179,12 +1267,12 @@
         <f>N5/1000</f>
         <v>1092.0306760000003</v>
       </c>
-      <c r="P5" s="2">
+      <c r="P5" s="17">
         <f>O5/64</f>
         <v>17.062979312500005</v>
       </c>
     </row>
-    <row r="6" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A6" s="10" t="s">
         <v>8</v>
       </c>
@@ -1232,12 +1320,12 @@
         <f>N6/1000</f>
         <v>2933.7679299999995</v>
       </c>
-      <c r="P6" s="5">
+      <c r="P6" s="17">
         <f>O6/64</f>
         <v>45.840123906249993</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A7" s="8" t="s">
         <v>9</v>
       </c>
@@ -1290,7 +1378,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A8" s="8" t="s">
         <v>10</v>
       </c>
@@ -1343,7 +1431,7 @@
         <v>85.082765468750011</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A9" s="8" t="s">
         <v>11</v>
       </c>
@@ -1396,7 +1484,7 @@
         <v>4.5718750000000002E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A10" s="8" t="s">
         <v>12</v>
       </c>
@@ -1441,7 +1529,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A11" s="8" t="s">
         <v>13</v>
       </c>
@@ -1486,17 +1574,17 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A12" s="8" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A13" s="8" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A14" s="8" t="s">
         <v>16</v>
       </c>
@@ -1504,7 +1592,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="15" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A15" s="11" t="s">
         <v>18</v>
       </c>
@@ -1549,7 +1637,7 @@
         <v>1952</v>
       </c>
     </row>
-    <row r="16" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A16" s="10" t="s">
         <v>19</v>
       </c>
@@ -1594,7 +1682,7 @@
         <v>5832</v>
       </c>
     </row>
-    <row r="17" spans="1:15" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A17" s="11" t="s">
         <v>20</v>
       </c>
@@ -1639,7 +1727,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="18" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A18" s="10" t="s">
         <v>21</v>
       </c>
@@ -1684,7 +1772,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="19" spans="1:15" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A19" s="11" t="s">
         <v>22</v>
       </c>
@@ -1733,7 +1821,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A20" s="8" t="s">
         <v>23</v>
       </c>
@@ -1782,7 +1870,7 @@
         <v>2933.7679499999999</v>
       </c>
     </row>
-    <row r="21" spans="1:15" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A21" s="11" t="s">
         <v>24</v>
       </c>
@@ -1830,8 +1918,12 @@
         <f t="shared" si="4"/>
         <v>270.47306600000002</v>
       </c>
-    </row>
-    <row r="22" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="P21" s="17">
+        <f>O21/64</f>
+        <v>4.2261416562500003</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A22" s="10" t="s">
         <v>25</v>
       </c>
@@ -1880,17 +1972,17 @@
         <v>42.451341140000004</v>
       </c>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A23" s="8" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A24" s="8" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A25" s="8" t="s">
         <v>27</v>
       </c>
@@ -1898,7 +1990,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A26" s="8" t="s">
         <v>29</v>
       </c>
@@ -1943,7 +2035,7 @@
         <v>7300</v>
       </c>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A27" s="8" t="s">
         <v>30</v>
       </c>
@@ -1988,7 +2080,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A28" s="8" t="s">
         <v>31</v>
       </c>
@@ -2033,7 +2125,7 @@
         <v>894120.09299999988</v>
       </c>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A29" s="8" t="s">
         <v>32</v>
       </c>
@@ -2078,7 +2170,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A30" s="8" t="s">
         <v>33</v>
       </c>
@@ -2099,7 +2191,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>15</v>
       </c>
@@ -2143,7 +2235,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:16" x14ac:dyDescent="0.35">
       <c r="B32" s="1">
         <v>31</v>
       </c>
@@ -2185,7 +2277,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A33" s="8" t="s">
         <v>49</v>
       </c>
@@ -2241,5 +2333,244 @@
   </sheetData>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46F5146F-D48F-4BC3-95FD-B5A4EAEFD094}">
+  <dimension ref="A1:E13"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="2" max="2" width="17.7265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.54296875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.08984375" style="1" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="C1" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="D1" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B2" s="1">
+        <v>100491.48</v>
+      </c>
+      <c r="C2" s="19">
+        <v>646983.25</v>
+      </c>
+      <c r="D2" s="1">
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <v>126.74</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B3" s="1">
+        <v>89458.335999999996</v>
+      </c>
+      <c r="C3" s="19">
+        <v>486963.38</v>
+      </c>
+      <c r="D3" s="1">
+        <v>0</v>
+      </c>
+      <c r="E3">
+        <v>132.68</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>36</v>
+      </c>
+      <c r="B4" s="1">
+        <v>99931.520000000004</v>
+      </c>
+      <c r="C4" s="19">
+        <v>368457.72</v>
+      </c>
+      <c r="D4" s="1">
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <v>163.68</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B5" s="1">
+        <v>90536.45</v>
+      </c>
+      <c r="C5" s="19">
+        <v>202264.06</v>
+      </c>
+      <c r="D5" s="1">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>162.94</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B6" s="1">
+        <v>91076.63</v>
+      </c>
+      <c r="C6" s="19">
+        <v>85966.63</v>
+      </c>
+      <c r="D6" s="1">
+        <v>0</v>
+      </c>
+      <c r="E6">
+        <v>174.08</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B7" s="1">
+        <v>81263.11</v>
+      </c>
+      <c r="C7" s="19">
+        <v>0</v>
+      </c>
+      <c r="D7" s="1">
+        <v>16355.625</v>
+      </c>
+      <c r="E7">
+        <v>178.35</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>40</v>
+      </c>
+      <c r="B8" s="1">
+        <v>83667.55</v>
+      </c>
+      <c r="C8" s="19">
+        <v>0</v>
+      </c>
+      <c r="D8" s="1">
+        <v>108223.734</v>
+      </c>
+      <c r="E8">
+        <v>203.97</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>41</v>
+      </c>
+      <c r="B9" s="1">
+        <v>83281.23</v>
+      </c>
+      <c r="C9" s="19">
+        <v>0</v>
+      </c>
+      <c r="D9" s="1">
+        <v>99330.32</v>
+      </c>
+      <c r="E9">
+        <v>198.07</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>42</v>
+      </c>
+      <c r="B10" s="1">
+        <v>83395.64</v>
+      </c>
+      <c r="C10" s="19">
+        <v>0</v>
+      </c>
+      <c r="D10" s="1">
+        <v>46563.387000000002</v>
+      </c>
+      <c r="E10">
+        <v>174.07</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>43</v>
+      </c>
+      <c r="B11" s="1">
+        <v>90779.4</v>
+      </c>
+      <c r="C11" s="19">
+        <v>85971.87</v>
+      </c>
+      <c r="D11" s="1">
+        <v>0</v>
+      </c>
+      <c r="E11">
+        <v>162.1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>44</v>
+      </c>
+      <c r="B12" s="1">
+        <v>95113.3</v>
+      </c>
+      <c r="C12" s="19">
+        <v>398250.22</v>
+      </c>
+      <c r="D12" s="1">
+        <v>0</v>
+      </c>
+      <c r="E12">
+        <v>124.49</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>45</v>
+      </c>
+      <c r="B13" s="1">
+        <v>103036.03</v>
+      </c>
+      <c r="C13" s="19">
+        <v>658910.80000000005</v>
+      </c>
+      <c r="D13" s="1">
+        <v>0</v>
+      </c>
+      <c r="E13">
+        <v>126.1</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="18" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
 </file>